--- a/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626947084</v>
+        <v>10.84497634407833</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890717232787</v>
+        <v>37.7890719832468</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.148685871697774</v>
+        <v>6.649377200863646</v>
       </c>
       <c r="C2" t="n">
-        <v>3.384084336538756</v>
+        <v>11.4177258003904</v>
       </c>
       <c r="D2" t="n">
-        <v>30.05129722699487</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.88744317137688</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C3" t="n">
-        <v>20.93576979306323</v>
+        <v>19.06063167795183</v>
       </c>
       <c r="D3" t="n">
-        <v>77.75441817634739</v>
+        <v>73.29728359906686</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.40378571054848</v>
+        <v>37.45858365553705</v>
       </c>
       <c r="C4" t="n">
-        <v>76.257252927371</v>
+        <v>58.81061447520093</v>
       </c>
       <c r="D4" t="n">
-        <v>102.4846428463245</v>
+        <v>104.4245763099162</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.89670517353839</v>
+        <v>43.4914232981337</v>
       </c>
       <c r="C5" t="n">
-        <v>142.0343491119073</v>
+        <v>94.02688637423827</v>
       </c>
       <c r="D5" t="n">
-        <v>73.63107781851079</v>
+        <v>81.06781667818038</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.06927178530758</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>169.0569546713008</v>
+        <v>120.3927027194906</v>
       </c>
       <c r="D6" t="n">
-        <v>46.73217246985243</v>
+        <v>52.64916588334796</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.8235317596096</v>
+        <v>28.92523261022377</v>
       </c>
       <c r="C7" t="n">
-        <v>154.1481340346087</v>
+        <v>115.7009304408951</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>105.7293190088602</v>
+        <v>77.60715602071035</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>53.36093296892687</v>
+        <v>43.59843379789659</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.45533531278805</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.625949274342265</v>
+        <v>7.670043780378234</v>
       </c>
       <c r="C21" t="n">
-        <v>91.51139129210718</v>
+        <v>94.91679178218065</v>
       </c>
       <c r="D21" t="n">
-        <v>7.625949274342265</v>
+        <v>7.670043780378234</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.597745483166066</v>
+        <v>8.346818981506383</v>
       </c>
       <c r="C2" t="n">
-        <v>10.02855279888117</v>
+        <v>11.77311846932775</v>
       </c>
       <c r="D2" t="n">
-        <v>26.18026602914969</v>
+        <v>27.44868406303657</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8839170911874</v>
+        <v>19.78712497909446</v>
       </c>
       <c r="C3" t="n">
-        <v>17.21494599396782</v>
+        <v>32.16696352964674</v>
       </c>
       <c r="D3" t="n">
-        <v>81.93175465791757</v>
+        <v>78.47600273896879</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.44658169890783</v>
+        <v>35.19958218806514</v>
       </c>
       <c r="C4" t="n">
-        <v>64.29858414194059</v>
+        <v>52.65898336039042</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6730405945487</v>
+        <v>115.2984138821539</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.59651136021713</v>
+        <v>49.06284151973436</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7026983143211</v>
+        <v>99.94191629232532</v>
       </c>
       <c r="D5" t="n">
-        <v>88.45546815263762</v>
+        <v>96.21127501618744</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.87809302488671</v>
+        <v>49.10702016642546</v>
       </c>
       <c r="C6" t="n">
-        <v>194.45574952787</v>
+        <v>134.4405306195582</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>37.54890444432775</v>
       </c>
       <c r="C7" t="n">
-        <v>192.6552242382813</v>
+        <v>142.4702450925929</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.28076414788136</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="C8" t="n">
-        <v>148.4549790976814</v>
+        <v>113.5734831657923</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>87.41874257695295</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.791041482120228</v>
+        <v>7.848238005756392</v>
       </c>
       <c r="C21" t="n">
-        <v>99.33577889703291</v>
+        <v>103.0081238255526</v>
       </c>
       <c r="D21" t="n">
-        <v>8.764921667385257</v>
+        <v>8.829267756475941</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.089200172366218</v>
+        <v>8.540223279243003</v>
       </c>
       <c r="C2" t="n">
-        <v>11.27733587868311</v>
+        <v>8.986918484675302</v>
       </c>
       <c r="D2" t="n">
-        <v>31.20681427489336</v>
+        <v>37.53123298565131</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.09284942574272</v>
+        <v>23.13488465057609</v>
       </c>
       <c r="C3" t="n">
-        <v>26.42864819832414</v>
+        <v>38.17525947963722</v>
       </c>
       <c r="D3" t="n">
-        <v>82.29991004701012</v>
+        <v>80.50331174823845</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.99988649347554</v>
+        <v>35.83771819582557</v>
       </c>
       <c r="C4" t="n">
-        <v>54.45852690227482</v>
+        <v>64.43897406364789</v>
       </c>
       <c r="D4" t="n">
-        <v>123.3006394194697</v>
+        <v>123.4537920613322</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.25919106058372</v>
+        <v>50.21639507222437</v>
       </c>
       <c r="C5" t="n">
-        <v>129.1243668010618</v>
+        <v>98.42020735074277</v>
       </c>
       <c r="D5" t="n">
-        <v>102.6662661716102</v>
+        <v>111.3547333541945</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.23156325614456</v>
+        <v>55.94980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>206.1287297313646</v>
+        <v>143.819166438228</v>
       </c>
       <c r="D6" t="n">
-        <v>67.86429180376503</v>
+        <v>75.31084814047708</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.13076203777662</v>
+        <v>46.17257627843174</v>
       </c>
       <c r="C7" t="n">
-        <v>226.6708186950248</v>
+        <v>164.0893112878119</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="C8" t="n">
-        <v>190.4296021927538</v>
+        <v>146.7860080004618</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>125.2484268646953</v>
+        <v>97.95780418204245</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>68.18728679846222</v>
+        <v>56.94136684631501</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.940601740019124</v>
+        <v>8.011037266353659</v>
       </c>
       <c r="C21" t="n">
-        <v>106.2055482727558</v>
+        <v>111.153142070657</v>
       </c>
       <c r="D21" t="n">
-        <v>9.925752175023906</v>
+        <v>10.01379658294207</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.684720118216532</v>
+        <v>7.865762606425444</v>
       </c>
       <c r="C2" t="n">
-        <v>7.938411936539709</v>
+        <v>6.182065293642165</v>
       </c>
       <c r="D2" t="n">
-        <v>25.91323065359456</v>
+        <v>30.79742548222244</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.07736244665303</v>
+        <v>26.32556468937822</v>
       </c>
       <c r="C3" t="n">
-        <v>40.0307626406637</v>
+        <v>51.9099098620501</v>
       </c>
       <c r="D3" t="n">
-        <v>89.2899537012474</v>
+        <v>88.00386420868409</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.66208316775662</v>
+        <v>24.12154109334413</v>
       </c>
       <c r="C4" t="n">
-        <v>92.68287376712438</v>
+        <v>84.38710566623882</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7150758193821</v>
+        <v>120.6077054667207</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.66136346195964</v>
+        <v>31.51410130632262</v>
       </c>
       <c r="C5" t="n">
-        <v>123.1602494977624</v>
+        <v>85.92746781420209</v>
       </c>
       <c r="D5" t="n">
-        <v>67.15154297048184</v>
+        <v>74.93189352663781</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2933916371082</v>
+        <v>108.0756960220101</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>133.9064598684479</v>
+        <v>103.1846289594525</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>92.29410167624263</v>
+        <v>72.18299995474673</v>
       </c>
       <c r="D8" t="n">
-        <v>26.28629478120835</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>43.4874963073167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.28434698133308</v>
+        <v>4.812527246217865</v>
       </c>
       <c r="C2" t="n">
-        <v>4.045782289201105</v>
+        <v>3.317325492649972</v>
       </c>
       <c r="D2" t="n">
-        <v>19.05768643483908</v>
+        <v>21.40308170028471</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.10681487778043</v>
+        <v>27.38585220996478</v>
       </c>
       <c r="C3" t="n">
-        <v>36.30993884156828</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D3" t="n">
-        <v>89.44212459540566</v>
+        <v>92.75061435871741</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.58322455624739</v>
+        <v>35.23787034853076</v>
       </c>
       <c r="C4" t="n">
-        <v>98.45162327727863</v>
+        <v>109.1723082076538</v>
       </c>
       <c r="D4" t="n">
-        <v>132.0303400056323</v>
+        <v>133.6767309056542</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.65569395991241</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="C5" t="n">
-        <v>148.1702722634499</v>
+        <v>118.202423591316</v>
       </c>
       <c r="D5" t="n">
-        <v>84.50393364304422</v>
+        <v>93.6832746777519</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.37491411649783</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>175.6179745787822</v>
+        <v>125.9876828859932</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>43.23027840880406</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>165.9457961965426</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4162646643925</v>
+        <v>95.13135254151592</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>54.69218285588555</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.787001805907448</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="C2" t="n">
-        <v>10.08843940884022</v>
+        <v>8.693375921105506</v>
       </c>
       <c r="D2" t="n">
-        <v>14.90980238439631</v>
+        <v>19.51910785583508</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3453385121834</v>
+        <v>21.84879515801277</v>
       </c>
       <c r="C3" t="n">
-        <v>25.86414326838222</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="D3" t="n">
-        <v>85.08316478854982</v>
+        <v>88.45546815263762</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.84972015245478</v>
+        <v>43.17628228507048</v>
       </c>
       <c r="C4" t="n">
-        <v>94.495180029164</v>
+        <v>102.4846428463245</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1767025290231</v>
+        <v>147.1414006693992</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.86524818927349</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>163.6573422979433</v>
+        <v>160.0248757922301</v>
       </c>
       <c r="D5" t="n">
-        <v>107.9431600819368</v>
+        <v>115.9198601789422</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>40.6139207769863</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7601734316445</v>
+        <v>154.7273651801143</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>58.52590764096936</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="C7" t="n">
-        <v>206.7285775786594</v>
+        <v>153.9085875947725</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>163.8929617469625</v>
+        <v>128.5107744859075</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>92.2999921624681</v>
+        <v>77.87811838708245</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.21538796232432</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.89615572752809</v>
+        <v>2.735149104031614</v>
       </c>
       <c r="C2" t="n">
-        <v>4.880267837810894</v>
+        <v>4.064435495581795</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42321537598839</v>
+        <v>13.60996842397353</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67422399310608</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="C3" t="n">
-        <v>33.02108403234147</v>
+        <v>30.37036523087508</v>
       </c>
       <c r="D3" t="n">
-        <v>82.07901681355457</v>
+        <v>87.42463306317848</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.55090899746525</v>
+        <v>47.23482729442679</v>
       </c>
       <c r="C4" t="n">
-        <v>93.21890801364314</v>
+        <v>97.85177542998383</v>
       </c>
       <c r="D4" t="n">
-        <v>152.578319455518</v>
+        <v>157.4664412749629</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.43604451606839</v>
+        <v>44.8167826988669</v>
       </c>
       <c r="C5" t="n">
-        <v>194.2633269778377</v>
+        <v>193.1097734253476</v>
       </c>
       <c r="D5" t="n">
-        <v>113.1464229144449</v>
+        <v>122.1539581009094</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>33.2881194078966</v>
       </c>
       <c r="C6" t="n">
-        <v>243.2005047914284</v>
+        <v>188.5790077702486</v>
       </c>
       <c r="D6" t="n">
-        <v>50.35482149852316</v>
+        <v>56.95609306187872</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>215.5319092426405</v>
+        <v>163.3706719683032</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>96.38308086443061</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.48041878474196</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.176935570942678</v>
+        <v>4.345215338996383</v>
       </c>
       <c r="C2" t="n">
-        <v>9.180322782411924</v>
+        <v>3.876921684070654</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68774747678728</v>
+        <v>12.12752939056085</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.02564861349743</v>
+        <v>15.67360209830033</v>
       </c>
       <c r="C3" t="n">
-        <v>25.84941705281852</v>
+        <v>22.99743997198154</v>
       </c>
       <c r="D3" t="n">
-        <v>72.8554971321558</v>
+        <v>79.75227475448963</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.48334833232148</v>
+        <v>44.74609686416112</v>
       </c>
       <c r="C4" t="n">
-        <v>88.77748139963056</v>
+        <v>87.85856554845556</v>
       </c>
       <c r="D4" t="n">
-        <v>157.2750004726348</v>
+        <v>163.4011061471349</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.14905539125883</v>
+        <v>55.64055113818799</v>
       </c>
       <c r="C5" t="n">
-        <v>185.5994034878595</v>
+        <v>188.7655398340555</v>
       </c>
       <c r="D5" t="n">
-        <v>135.6529890343031</v>
+        <v>144.439630987312</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.29819892684633</v>
+        <v>43.47178834404877</v>
       </c>
       <c r="C6" t="n">
-        <v>273.8320149116332</v>
+        <v>241.5904385564637</v>
       </c>
       <c r="D6" t="n">
-        <v>68.34731167425446</v>
+        <v>75.47185476397357</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>275.538292421614</v>
+        <v>210.8008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>180.4157756094363</v>
+        <v>146.7025594456009</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>71.1109314617092</v>
+        <v>63.45624461169682</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.215804568485051</v>
+        <v>2.974695543867836</v>
       </c>
       <c r="C2" t="n">
-        <v>5.448699758569798</v>
+        <v>2.301216618754523</v>
       </c>
       <c r="D2" t="n">
-        <v>12.52317371537231</v>
+        <v>9.770353152664256</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.4057649014902</v>
+        <v>15.42816517223863</v>
       </c>
       <c r="C3" t="n">
-        <v>30.67470701919159</v>
+        <v>19.62513660789374</v>
       </c>
       <c r="D3" t="n">
-        <v>70.19005211512571</v>
+        <v>73.1156602737812</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.89702396870788</v>
+        <v>40.15151760828606</v>
       </c>
       <c r="C4" t="n">
-        <v>80.34132337703772</v>
+        <v>77.23998237932204</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0152382416369</v>
+        <v>167.4724138766464</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.98416283467437</v>
+        <v>60.84381397069608</v>
       </c>
       <c r="C5" t="n">
-        <v>183.7095391571844</v>
+        <v>183.218665305061</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7291076913446</v>
+        <v>159.3621960918635</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.65796055495717</v>
+        <v>52.04539104523617</v>
       </c>
       <c r="C6" t="n">
-        <v>294.2798560956857</v>
+        <v>274.9993129319826</v>
       </c>
       <c r="D6" t="n">
-        <v>80.70457002760907</v>
+        <v>90.72723234026475</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>324.0464464884489</v>
+        <v>258.0514023135698</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>227.3138634413064</v>
+        <v>186.3406230045658</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>77.98905587766234</v>
+        <v>71.99843138634832</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.980586030093316</v>
+        <v>4.402156705842698</v>
       </c>
       <c r="C2" t="n">
-        <v>15.58524480491811</v>
+        <v>2.849031837724244</v>
       </c>
       <c r="D2" t="n">
-        <v>12.21294144083032</v>
+        <v>9.946085991724436</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.63723637551419</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44828315240908</v>
+        <v>14.59858836215007</v>
       </c>
       <c r="D3" t="n">
-        <v>65.45802818065609</v>
+        <v>65.52184178143213</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47286790274425</v>
+        <v>35.21234490822035</v>
       </c>
       <c r="C4" t="n">
-        <v>78.42691535375644</v>
+        <v>64.55383854504477</v>
       </c>
       <c r="D4" t="n">
-        <v>154.9777108446972</v>
+        <v>165.6345821742964</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.54237636776331</v>
+        <v>60.50020227420971</v>
       </c>
       <c r="C5" t="n">
-        <v>168.664255589602</v>
+        <v>165.4244881655876</v>
       </c>
       <c r="D5" t="n">
-        <v>167.5597894223244</v>
+        <v>176.3709750679395</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.55986789999051</v>
+        <v>63.1950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>294.4408627191822</v>
+        <v>282.4458692686947</v>
       </c>
       <c r="D6" t="n">
-        <v>100.6291396852981</v>
+        <v>110.8530602773244</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>364.0507019410979</v>
+        <v>316.7402800734442</v>
       </c>
       <c r="D7" t="n">
-        <v>51.2030515149924</v>
+        <v>56.53295980134833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>301.9168714870216</v>
+        <v>245.6725455107218</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>148.9890498487916</v>
+        <v>129.4640515067311</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>50.1084028247572</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.503096792930871</v>
+        <v>4.863578126838698</v>
       </c>
       <c r="C2" t="n">
-        <v>14.35216968838412</v>
+        <v>7.929576207201487</v>
       </c>
       <c r="D2" t="n">
-        <v>5.996514977539517</v>
+        <v>13.49215869946391</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.179479903427919</v>
+        <v>3.147483139815274</v>
       </c>
       <c r="C2" t="n">
-        <v>9.102764713776425</v>
+        <v>1.64050041379642</v>
       </c>
       <c r="D2" t="n">
-        <v>9.086075002804231</v>
+        <v>7.320892630568465</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15680189523901</v>
+        <v>17.23458094805276</v>
       </c>
       <c r="C3" t="n">
-        <v>40.22220344299183</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="D3" t="n">
-        <v>70.83309686140737</v>
+        <v>70.36185796336891</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.7678752401038</v>
+        <v>46.78813208899449</v>
       </c>
       <c r="C4" t="n">
-        <v>109.0957318867226</v>
+        <v>92.8615518492973</v>
       </c>
       <c r="D4" t="n">
-        <v>157.7855092788431</v>
+        <v>169.8845679859808</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.93763547748049</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>251.1310627463342</v>
+        <v>241.4117604742907</v>
       </c>
       <c r="D5" t="n">
-        <v>151.2873212244335</v>
+        <v>160.0985068700486</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.83148355223482</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>291.703750119742</v>
+        <v>263.9703592224739</v>
       </c>
       <c r="D6" t="n">
-        <v>77.645444181176</v>
+        <v>86.70206675285282</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2980323048515</v>
+        <v>172.7728697318749</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>109.8182981970482</v>
+        <v>95.38169820609886</v>
       </c>
       <c r="D8" t="n">
-        <v>23.78283813537898</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>38.162496759482</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.626036240139976</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.33169185531518</v>
+        <v>7.674321804097318</v>
       </c>
       <c r="C2" t="n">
-        <v>7.112762117268142</v>
+        <v>7.044039777970864</v>
       </c>
       <c r="D2" t="n">
-        <v>18.92220525165302</v>
+        <v>24.53682037224053</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.81319019875262</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C3" t="n">
-        <v>36.16267668593126</v>
+        <v>19.97856578142259</v>
       </c>
       <c r="D3" t="n">
-        <v>8.173049637854696</v>
+        <v>14.47096116059799</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39739269507999</v>
+        <v>13.39748979805922</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13929116835996</v>
+        <v>70.13979953101592</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576163846479999</v>
+        <v>1.576175270359908</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.566509483079415</v>
+        <v>4.902848035008571</v>
       </c>
       <c r="C2" t="n">
-        <v>8.575566196595888</v>
+        <v>5.558655501445441</v>
       </c>
       <c r="D2" t="n">
-        <v>35.48134377918397</v>
+        <v>26.61321676672253</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.71978529812893</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C3" t="n">
-        <v>30.89069151412589</v>
+        <v>24.66641106920111</v>
       </c>
       <c r="D3" t="n">
-        <v>22.08932334555324</v>
+        <v>31.58282364561989</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.04273923509713</v>
+        <v>12.1118214272929</v>
       </c>
       <c r="C4" t="n">
-        <v>55.64545987670921</v>
+        <v>31.00064725700153</v>
       </c>
       <c r="D4" t="n">
-        <v>19.34828375529614</v>
+        <v>22.65382827549515</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43615283754409</v>
+        <v>15.43767613354432</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11748425156176</v>
+        <v>86.12598263977358</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249716386851387</v>
+        <v>3.250037080746173</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.098215828153687</v>
+        <v>4.37368602241954</v>
       </c>
       <c r="C2" t="n">
-        <v>7.765624340592271</v>
+        <v>6.497206306705391</v>
       </c>
       <c r="D2" t="n">
-        <v>26.33930915723768</v>
+        <v>26.36188935443535</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.86566479543421</v>
+        <v>18.28505099159684</v>
       </c>
       <c r="C3" t="n">
-        <v>32.3485868549324</v>
+        <v>22.84036033930204</v>
       </c>
       <c r="D3" t="n">
-        <v>45.34692645916017</v>
+        <v>45.54327600000953</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.40530723760046</v>
+        <v>27.13354304997335</v>
       </c>
       <c r="C4" t="n">
-        <v>68.21673922958962</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>26.06147455693583</v>
+        <v>33.37451320587032</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.64629308903067</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>59.93569734426779</v>
+        <v>34.97476196379262</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>30.80233422074368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.717995134913</v>
+        <v>16.72644570878471</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1438705662237</v>
+        <v>102.0313188235867</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179498783728251</v>
+        <v>4.181611427196176</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.550220682734719</v>
+        <v>5.069745144730529</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32838675930394</v>
+        <v>5.359360717483338</v>
       </c>
       <c r="D2" t="n">
-        <v>28.22917348791279</v>
+        <v>26.05165707989336</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48140053244621</v>
+        <v>16.45900026169778</v>
       </c>
       <c r="C3" t="n">
-        <v>31.05758862384785</v>
+        <v>24.16081100151401</v>
       </c>
       <c r="D3" t="n">
-        <v>54.65880343394117</v>
+        <v>55.44911033585985</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.82120841130262</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>74.36837034440013</v>
+        <v>52.76108512163209</v>
       </c>
       <c r="D4" t="n">
-        <v>40.87899265713293</v>
+        <v>47.86020058203201</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>25.69724615866027</v>
       </c>
       <c r="C5" t="n">
-        <v>94.93500300066657</v>
+        <v>64.45173678380311</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49584901056943</v>
+        <v>35.31837366027901</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>54.29948377418685</v>
+        <v>34.61642405174254</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02594905996442</v>
+        <v>18.04541877556125</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7394796264363</v>
+        <v>117.7248748691377</v>
       </c>
       <c r="D21" t="n">
-        <v>6.008649686654807</v>
+        <v>6.01513959185375</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.383323573012761</v>
+        <v>6.985134915716055</v>
       </c>
       <c r="C2" t="n">
-        <v>9.13221714490383</v>
+        <v>6.57770961845363</v>
       </c>
       <c r="D2" t="n">
-        <v>31.47974013667397</v>
+        <v>28.44908497366407</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C3" t="n">
-        <v>35.78470381979624</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="D3" t="n">
-        <v>59.53808952404782</v>
+        <v>59.19447782756144</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.96388062358789</v>
+        <v>23.04947260030661</v>
       </c>
       <c r="C4" t="n">
-        <v>63.53282093262809</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D4" t="n">
-        <v>49.45554060143307</v>
+        <v>55.81137523872692</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.93010029101601</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C5" t="n">
-        <v>85.95201150680826</v>
+        <v>61.04016351154545</v>
       </c>
       <c r="D5" t="n">
-        <v>31.95588777323368</v>
+        <v>35.39200473809752</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.6050596854523</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>69.59511300635215</v>
+        <v>46.73217246985243</v>
       </c>
       <c r="D6" t="n">
-        <v>30.06798693796707</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>31.14103717870882</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>27.95035713990669</v>
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.036587112310133</v>
+        <v>7.050195035644554</v>
       </c>
       <c r="C21" t="n">
-        <v>65.9680041779075</v>
+        <v>66.97685283862326</v>
       </c>
       <c r="D21" t="n">
-        <v>4.397866945193833</v>
+        <v>4.406371897277847</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.94015444776995</v>
+        <v>5.970007789524853</v>
       </c>
       <c r="C2" t="n">
-        <v>5.715735134124929</v>
+        <v>6.450082416901544</v>
       </c>
       <c r="D2" t="n">
-        <v>26.13117864393735</v>
+        <v>24.4249011339564</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.60688431214055</v>
+        <v>20.70505908256523</v>
       </c>
       <c r="C3" t="n">
-        <v>35.67671157232909</v>
+        <v>23.99391389179205</v>
       </c>
       <c r="D3" t="n">
-        <v>71.59395133219864</v>
+        <v>68.78615289805276</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.37076614150258</v>
+        <v>27.01867856857647</v>
       </c>
       <c r="C4" t="n">
-        <v>79.48622112663875</v>
+        <v>50.51484637431538</v>
       </c>
       <c r="D4" t="n">
-        <v>69.18670596138547</v>
+        <v>73.34735273198346</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.75953823238432</v>
+        <v>29.67332436085985</v>
       </c>
       <c r="C5" t="n">
-        <v>104.6788489653162</v>
+        <v>77.18991324640548</v>
       </c>
       <c r="D5" t="n">
-        <v>43.09872421643498</v>
+        <v>48.81740459367266</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>22.42017232188442</v>
       </c>
       <c r="C6" t="n">
-        <v>107.7939344308913</v>
+        <v>76.35739119320418</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>69.82778721225863</v>
+        <v>48.92736033654828</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.55288818840698</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.248253744533574</v>
+        <v>7.269696649475422</v>
       </c>
       <c r="C21" t="n">
-        <v>75.20063259953584</v>
+        <v>76.33181481949194</v>
       </c>
       <c r="D21" t="n">
-        <v>5.436190308400181</v>
+        <v>5.452272487106567</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.01084028247572</v>
+        <v>4.434554380082843</v>
       </c>
       <c r="C2" t="n">
-        <v>3.836670028196535</v>
+        <v>3.788564390688441</v>
       </c>
       <c r="D2" t="n">
-        <v>25.84647180970578</v>
+        <v>22.68328070662255</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="C3" t="n">
-        <v>27.87181732356694</v>
+        <v>24.63695863807371</v>
       </c>
       <c r="D3" t="n">
-        <v>75.53075962622836</v>
+        <v>72.36462328003239</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.69732827411827</v>
+        <v>34.66354794154638</v>
       </c>
       <c r="C4" t="n">
-        <v>84.96142807322322</v>
+        <v>55.58164627593317</v>
       </c>
       <c r="D4" t="n">
-        <v>88.40736251512952</v>
+        <v>91.36831359113789</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.5398887885403</v>
+        <v>35.58835427894688</v>
       </c>
       <c r="C5" t="n">
-        <v>127.4553957038422</v>
+        <v>86.49197274414401</v>
       </c>
       <c r="D5" t="n">
-        <v>56.91682315370885</v>
+        <v>63.66633862040567</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.93214590188251</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="C6" t="n">
-        <v>137.4594048101172</v>
+        <v>101.9976959850181</v>
       </c>
       <c r="D6" t="n">
-        <v>39.36611944488861</v>
+        <v>43.79380159104173</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.00212772632452</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>115.0421777313455</v>
+        <v>82.46386191361933</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>62.83676181031709</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>33.88011327355743</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.444941820606962</v>
+        <v>7.476700346555594</v>
       </c>
       <c r="C21" t="n">
-        <v>83.75559548182832</v>
+        <v>85.98205398538933</v>
       </c>
       <c r="D21" t="n">
-        <v>6.514324093031092</v>
+        <v>6.542112803236145</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634407833</v>
+        <v>10.84497664364786</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890719832468</v>
+        <v>37.78907302708998</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.649377200863646</v>
+        <v>5.91895690890402</v>
       </c>
       <c r="C2" t="n">
-        <v>11.4177258003904</v>
+        <v>5.282784396552087</v>
       </c>
       <c r="D2" t="n">
-        <v>29.52409870981433</v>
+        <v>18.9133695223148</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.67636741496382</v>
+        <v>18.32922963828795</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06063167795183</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="D3" t="n">
-        <v>73.29728359906686</v>
+        <v>53.9863062565321</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.45858365553705</v>
+        <v>37.30543101367455</v>
       </c>
       <c r="C4" t="n">
-        <v>58.81061447520093</v>
+        <v>55.83690067903733</v>
       </c>
       <c r="D4" t="n">
-        <v>104.4245763099162</v>
+        <v>67.74451858384691</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.4914232981337</v>
+        <v>47.41841411512095</v>
       </c>
       <c r="C5" t="n">
-        <v>94.02688637423827</v>
+        <v>93.97779898902593</v>
       </c>
       <c r="D5" t="n">
-        <v>81.06781667818038</v>
+        <v>51.49266708774522</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>45.56487444950297</v>
       </c>
       <c r="C6" t="n">
-        <v>120.3927027194906</v>
+        <v>104.6140536168359</v>
       </c>
       <c r="D6" t="n">
-        <v>52.64916588334796</v>
+        <v>41.41895389446869</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.92523261022377</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7009304408951</v>
+        <v>101.6874637104761</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C8" t="n">
-        <v>77.60715602071035</v>
+        <v>70.93127163183205</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.670043780378234</v>
+        <v>7.710665408213788</v>
       </c>
       <c r="C21" t="n">
-        <v>94.91679178218065</v>
+        <v>95.41948442664562</v>
       </c>
       <c r="D21" t="n">
-        <v>7.670043780378234</v>
+        <v>8.674498584240512</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.346818981506383</v>
+        <v>9.542587685278997</v>
       </c>
       <c r="C2" t="n">
-        <v>11.77311846932775</v>
+        <v>15.00503191170825</v>
       </c>
       <c r="D2" t="n">
-        <v>27.44868406303657</v>
+        <v>21.03983504971339</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78712497909446</v>
+        <v>19.08026663203676</v>
       </c>
       <c r="C3" t="n">
-        <v>32.16696352964674</v>
+        <v>20.84741249968102</v>
       </c>
       <c r="D3" t="n">
-        <v>78.47600273896879</v>
+        <v>56.11179003622645</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.19958218806514</v>
+        <v>35.8887690764464</v>
       </c>
       <c r="C4" t="n">
-        <v>52.65898336039042</v>
+        <v>54.57339138367169</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2984138821539</v>
+        <v>78.22271183127312</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>99.94191629232532</v>
+        <v>97.53663441692063</v>
       </c>
       <c r="D5" t="n">
-        <v>96.21127501618744</v>
+        <v>62.26734814185396</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.10702016642546</v>
+        <v>55.10451689166923</v>
       </c>
       <c r="C6" t="n">
-        <v>134.4405306195582</v>
+        <v>126.8329676593497</v>
       </c>
       <c r="D6" t="n">
-        <v>64.24164277509429</v>
+        <v>47.85921883432777</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.54890444432775</v>
+        <v>43.17824578047897</v>
       </c>
       <c r="C7" t="n">
-        <v>142.4702450925929</v>
+        <v>125.4624478642211</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="C8" t="n">
-        <v>113.5734831657923</v>
+        <v>102.725171033865</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>12.7578114166873</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>63.5671821022767</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.848238005756392</v>
+        <v>7.899725393321537</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0081238255526</v>
+        <v>104.6713614615104</v>
       </c>
       <c r="D21" t="n">
-        <v>8.829267756475941</v>
+        <v>9.874656741651922</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.540223279243003</v>
+        <v>8.887761966546375</v>
       </c>
       <c r="C2" t="n">
-        <v>8.986918484675302</v>
+        <v>11.47859415805371</v>
       </c>
       <c r="D2" t="n">
-        <v>37.53123298565131</v>
+        <v>35.73168944376691</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.13488465057609</v>
+        <v>25.01984024272996</v>
       </c>
       <c r="C3" t="n">
-        <v>38.17525947963722</v>
+        <v>39.21591204613884</v>
       </c>
       <c r="D3" t="n">
-        <v>80.50331174823845</v>
+        <v>58.7134214524805</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.83771819582557</v>
+        <v>35.86324363613598</v>
       </c>
       <c r="C4" t="n">
-        <v>64.43897406364789</v>
+        <v>53.25883120768522</v>
       </c>
       <c r="D4" t="n">
-        <v>123.4537920613322</v>
+        <v>85.48469959958678</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.21639507222437</v>
+        <v>52.327152636355</v>
       </c>
       <c r="C5" t="n">
-        <v>98.42020735074277</v>
+        <v>97.83115872819468</v>
       </c>
       <c r="D5" t="n">
-        <v>111.3547333541945</v>
+        <v>73.90105843717866</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.94980166502573</v>
+        <v>61.46427851978007</v>
       </c>
       <c r="C6" t="n">
-        <v>143.819166438228</v>
+        <v>139.9147558184385</v>
       </c>
       <c r="D6" t="n">
-        <v>75.31084814047708</v>
+        <v>54.54099370943156</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.17257627843174</v>
+        <v>53.17930964364123</v>
       </c>
       <c r="C7" t="n">
-        <v>164.0893112878119</v>
+        <v>150.7944838769016</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>45.39405034896402</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.79113408536946</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7860080004618</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="C9" t="n">
-        <v>97.95780418204245</v>
+        <v>91.52342972840887</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>56.94136684631501</v>
+        <v>55.37547925804135</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.011037266353659</v>
+        <v>8.073454135064763</v>
       </c>
       <c r="C21" t="n">
-        <v>111.153142070657</v>
+        <v>113.0283578909067</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01379658294207</v>
+        <v>11.10099943571405</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.865762606425444</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C2" t="n">
-        <v>6.182065293642165</v>
+        <v>7.621307428067988</v>
       </c>
       <c r="D2" t="n">
-        <v>30.79742548222244</v>
+        <v>28.7494997711636</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.32556468937822</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="C3" t="n">
-        <v>51.9099098620501</v>
+        <v>53.51506735849363</v>
       </c>
       <c r="D3" t="n">
-        <v>88.00386420868409</v>
+        <v>65.32058350206152</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.12154109334413</v>
+        <v>25.12979598560561</v>
       </c>
       <c r="C4" t="n">
-        <v>84.38710566623882</v>
+        <v>79.00123776074084</v>
       </c>
       <c r="D4" t="n">
-        <v>120.6077054667207</v>
+        <v>82.81729108714818</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.51410130632262</v>
+        <v>34.60660657470007</v>
       </c>
       <c r="C5" t="n">
-        <v>85.92746781420209</v>
+        <v>83.59581701661591</v>
       </c>
       <c r="D5" t="n">
-        <v>74.93189352663781</v>
+        <v>53.16163818496479</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>33.00635781677777</v>
       </c>
       <c r="C6" t="n">
-        <v>108.0756960220101</v>
+        <v>99.30083504145215</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>29.86672865859647</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>103.1846289594525</v>
+        <v>93.06379187637214</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>72.18299995474673</v>
+        <v>67.42643232767094</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.812527246217865</v>
+        <v>4.861614631430205</v>
       </c>
       <c r="C2" t="n">
-        <v>3.317325492649972</v>
+        <v>3.19166178650638</v>
       </c>
       <c r="D2" t="n">
-        <v>21.40308170028471</v>
+        <v>19.29428763156256</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.38585220996478</v>
+        <v>28.83393007372882</v>
       </c>
       <c r="C3" t="n">
-        <v>38.52377991464484</v>
+        <v>41.84208715499906</v>
       </c>
       <c r="D3" t="n">
-        <v>92.75061435871741</v>
+        <v>73.37091467688538</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.23787034853076</v>
+        <v>37.50963453615788</v>
       </c>
       <c r="C4" t="n">
-        <v>109.1723082076538</v>
+        <v>109.2488845285851</v>
       </c>
       <c r="D4" t="n">
-        <v>133.6767309056542</v>
+        <v>95.24818051832131</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>118.202423591316</v>
+        <v>114.7172192412398</v>
       </c>
       <c r="D5" t="n">
-        <v>93.6832746777519</v>
+        <v>65.80163987714248</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>39.80888765950392</v>
       </c>
       <c r="C6" t="n">
-        <v>125.9876828859932</v>
+        <v>117.7763450876729</v>
       </c>
       <c r="D6" t="n">
-        <v>43.23027840880406</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>116.719002810199</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>95.13135254151592</v>
+        <v>87.45408549430587</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.602433237509047</v>
+        <v>4.645630136495907</v>
       </c>
       <c r="C2" t="n">
-        <v>8.693375921105506</v>
+        <v>5.557673753741193</v>
       </c>
       <c r="D2" t="n">
-        <v>19.51910785583508</v>
+        <v>18.06415775814131</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.84879515801277</v>
+        <v>22.55565350507047</v>
       </c>
       <c r="C3" t="n">
-        <v>24.88730430265664</v>
+        <v>25.64325003492669</v>
       </c>
       <c r="D3" t="n">
-        <v>88.45546815263762</v>
+        <v>71.64794745593223</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.17628228507048</v>
+        <v>46.63497944713198</v>
       </c>
       <c r="C4" t="n">
-        <v>102.4846428463245</v>
+        <v>107.7811717107361</v>
       </c>
       <c r="D4" t="n">
-        <v>147.1414006693992</v>
+        <v>108.8532402037736</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>46.60847225911733</v>
       </c>
       <c r="C5" t="n">
-        <v>160.0248757922301</v>
+        <v>158.1104677689488</v>
       </c>
       <c r="D5" t="n">
-        <v>115.9198601789422</v>
+        <v>82.93313731624932</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6139207769863</v>
+        <v>45.48437113775474</v>
       </c>
       <c r="C6" t="n">
-        <v>154.7273651801143</v>
+        <v>150.1386764104647</v>
       </c>
       <c r="D6" t="n">
-        <v>58.52590764096936</v>
+        <v>46.4504108787336</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.06874770149305</v>
+        <v>33.17718191731671</v>
       </c>
       <c r="C7" t="n">
-        <v>153.9085875947725</v>
+        <v>142.4702450925929</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>128.5107744859075</v>
+        <v>119.9155733352267</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>77.87811838708245</v>
+        <v>76.65780599070366</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.735149104031614</v>
+        <v>2.75478405811655</v>
       </c>
       <c r="C2" t="n">
-        <v>4.064435495581795</v>
+        <v>2.547635292520473</v>
       </c>
       <c r="D2" t="n">
-        <v>13.60996842397353</v>
+        <v>12.46525060082175</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52972715413255</v>
+        <v>21.90770002026757</v>
       </c>
       <c r="C3" t="n">
-        <v>30.37036523087508</v>
+        <v>25.314364554004</v>
       </c>
       <c r="D3" t="n">
-        <v>87.42463306317848</v>
+        <v>72.01610284502478</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.23482729442679</v>
+        <v>51.47205038595602</v>
       </c>
       <c r="C4" t="n">
-        <v>97.85177542998383</v>
+        <v>102.7016090889631</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4664412749629</v>
+        <v>118.1955513573862</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.8167826988669</v>
+        <v>48.96466674930968</v>
       </c>
       <c r="C5" t="n">
-        <v>193.1097734253476</v>
+        <v>190.5081420090936</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1539581009094</v>
+        <v>90.41896356113125</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>39.48687441251096</v>
       </c>
       <c r="C6" t="n">
-        <v>188.5790077702486</v>
+        <v>187.7337229968921</v>
       </c>
       <c r="D6" t="n">
-        <v>56.95609306187872</v>
+        <v>46.249152599363</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3706719683032</v>
+        <v>153.6690411549362</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>96.38308086443061</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.77302065833652</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.345215338996383</v>
+        <v>3.279037332184346</v>
       </c>
       <c r="C2" t="n">
-        <v>3.876921684070654</v>
+        <v>3.086614782151972</v>
       </c>
       <c r="D2" t="n">
-        <v>12.12752939056085</v>
+        <v>11.73384856115788</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67360209830033</v>
+        <v>15.82577299245858</v>
       </c>
       <c r="C3" t="n">
-        <v>22.99743997198154</v>
+        <v>17.20512851692535</v>
       </c>
       <c r="D3" t="n">
-        <v>79.75227475448963</v>
+        <v>65.85563600087605</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.74609686416112</v>
+        <v>47.03062377194345</v>
       </c>
       <c r="C4" t="n">
-        <v>87.85856554845556</v>
+        <v>83.48095253521902</v>
       </c>
       <c r="D4" t="n">
-        <v>163.4011061471349</v>
+        <v>125.8659461706666</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.64055113818799</v>
+        <v>61.50649367106269</v>
       </c>
       <c r="C5" t="n">
-        <v>188.7655398340555</v>
+        <v>191.5880644837651</v>
       </c>
       <c r="D5" t="n">
-        <v>144.439630987312</v>
+        <v>108.6794708601219</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.47178834404877</v>
+        <v>50.71708640139023</v>
       </c>
       <c r="C6" t="n">
-        <v>241.5904385564637</v>
+        <v>241.6709418682119</v>
       </c>
       <c r="D6" t="n">
-        <v>75.47185476397357</v>
+        <v>60.78000036992004</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>22.87668500435917</v>
       </c>
       <c r="C7" t="n">
-        <v>210.8008670558751</v>
+        <v>208.2856294375948</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7025594456009</v>
+        <v>140.5273663858884</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>63.45624461169682</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.974695543867836</v>
+        <v>2.478912953223196</v>
       </c>
       <c r="C2" t="n">
-        <v>2.301216618754523</v>
+        <v>2.351285751671111</v>
       </c>
       <c r="D2" t="n">
-        <v>9.770353152664256</v>
+        <v>8.774860980557991</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.42816517223863</v>
+        <v>14.02426595516569</v>
       </c>
       <c r="C3" t="n">
-        <v>19.62513660789374</v>
+        <v>14.92747384307275</v>
       </c>
       <c r="D3" t="n">
-        <v>73.1156602737812</v>
+        <v>61.40831890063799</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.15151760828606</v>
+        <v>41.31292514241003</v>
       </c>
       <c r="C4" t="n">
-        <v>77.23998237932204</v>
+        <v>67.77004402415733</v>
       </c>
       <c r="D4" t="n">
-        <v>167.4724138766464</v>
+        <v>129.3374060528833</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.84381397069608</v>
+        <v>67.34789251133121</v>
       </c>
       <c r="C5" t="n">
-        <v>183.218665305061</v>
+        <v>183.3168400754857</v>
       </c>
       <c r="D5" t="n">
-        <v>159.3621960918635</v>
+        <v>122.816637801276</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.04539104523617</v>
+        <v>60.41773546705297</v>
       </c>
       <c r="C6" t="n">
-        <v>274.9993129319826</v>
+        <v>274.798054652612</v>
       </c>
       <c r="D6" t="n">
-        <v>90.72723234026475</v>
+        <v>71.3661858648134</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="C7" t="n">
-        <v>258.0514023135698</v>
+        <v>260.9858462015636</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>186.3406230045658</v>
+        <v>179.6647386156875</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>71.99843138634832</v>
+        <v>77.54530591534278</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.402156705842698</v>
+        <v>4.828235209485814</v>
       </c>
       <c r="C2" t="n">
-        <v>2.849031837724244</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="D2" t="n">
-        <v>9.946085991724436</v>
+        <v>11.56596970373167</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.81180754042088</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C3" t="n">
-        <v>14.59858836215007</v>
+        <v>12.20803270230909</v>
       </c>
       <c r="D3" t="n">
-        <v>65.52184178143213</v>
+        <v>55.72399969304897</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.21234490822035</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="C4" t="n">
-        <v>64.55383854504477</v>
+        <v>53.19501760690918</v>
       </c>
       <c r="D4" t="n">
-        <v>165.6345821742964</v>
+        <v>128.5205919629499</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.50020227420971</v>
+        <v>65.99798941799185</v>
       </c>
       <c r="C5" t="n">
-        <v>165.4244881655876</v>
+        <v>158.8713222397401</v>
       </c>
       <c r="D5" t="n">
-        <v>176.3709750679395</v>
+        <v>137.1992416684918</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.1950997223672</v>
+        <v>72.29197394991814</v>
       </c>
       <c r="C6" t="n">
-        <v>282.4458692686947</v>
+        <v>282.566624236317</v>
       </c>
       <c r="D6" t="n">
-        <v>110.8530602773244</v>
+        <v>87.90961642907641</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>316.7402800734442</v>
+        <v>317.3391461730347</v>
       </c>
       <c r="D7" t="n">
-        <v>56.53295980134833</v>
+        <v>50.18497914568845</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>245.6725455107218</v>
+        <v>248.0091050468292</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>129.4640515067311</v>
+        <v>131.2390513560093</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1084028247572</v>
+        <v>54.8060655895782</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.29148125717007</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.863578126838698</v>
+        <v>6.601271563355553</v>
       </c>
       <c r="C2" t="n">
-        <v>7.929576207201487</v>
+        <v>5.862997289761952</v>
       </c>
       <c r="D2" t="n">
-        <v>13.49215869946391</v>
+        <v>7.341509332357648</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.147483139815274</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C2" t="n">
-        <v>1.64050041379642</v>
+        <v>5.326963043243193</v>
       </c>
       <c r="D2" t="n">
-        <v>7.320892630568465</v>
+        <v>8.511752595819846</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23458094805276</v>
+        <v>16.10557108816893</v>
       </c>
       <c r="C3" t="n">
-        <v>15.80122929985241</v>
+        <v>21.72607669498191</v>
       </c>
       <c r="D3" t="n">
-        <v>70.36185796336891</v>
+        <v>60.51492848977339</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.78813208899449</v>
+        <v>48.88121819444869</v>
       </c>
       <c r="C4" t="n">
-        <v>92.8615518492973</v>
+        <v>79.30754304446585</v>
       </c>
       <c r="D4" t="n">
-        <v>169.8845679859808</v>
+        <v>131.1752377552333</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>43.14781160164732</v>
       </c>
       <c r="C5" t="n">
-        <v>241.4117604742907</v>
+        <v>238.6137795171873</v>
       </c>
       <c r="D5" t="n">
-        <v>160.0985068700486</v>
+        <v>126.3509295365645</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.64280806657019</v>
+        <v>24.03023855684918</v>
       </c>
       <c r="C6" t="n">
-        <v>263.9703592224739</v>
+        <v>267.1502400365293</v>
       </c>
       <c r="D6" t="n">
-        <v>86.70206675285282</v>
+        <v>71.80895407942872</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>172.7728697318749</v>
+        <v>174.3898082007694</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>95.38169820609886</v>
+        <v>96.71687508387453</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.674321804097318</v>
+        <v>7.379797492823274</v>
       </c>
       <c r="C2" t="n">
-        <v>7.044039777970864</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="D2" t="n">
-        <v>24.53682037224053</v>
+        <v>9.206829970426588</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.33780332571891</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C3" t="n">
-        <v>19.97856578142259</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="D3" t="n">
-        <v>14.47096116059799</v>
+        <v>9.302059497738529</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39748979805922</v>
+        <v>13.39860218681659</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13979953101592</v>
+        <v>70.14562321333392</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576175270359908</v>
+        <v>1.576306139625481</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>4.666246838285089</v>
+      </c>
+      <c r="C2" t="n">
         <v>4.902848035008571</v>
       </c>
-      <c r="C2" t="n">
-        <v>5.558655501445441</v>
-      </c>
       <c r="D2" t="n">
-        <v>26.61321676672253</v>
+        <v>16.52183211476957</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="C3" t="n">
-        <v>24.66641106920111</v>
+        <v>21.78498155723672</v>
       </c>
       <c r="D3" t="n">
-        <v>31.58282364561989</v>
+        <v>14.78512042595696</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.1118214272929</v>
+        <v>16.25970547773567</v>
       </c>
       <c r="C4" t="n">
-        <v>31.00064725700153</v>
+        <v>23.40682876465245</v>
       </c>
       <c r="D4" t="n">
-        <v>22.65382827549515</v>
+        <v>19.94813160259094</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43767613354432</v>
+        <v>15.44323200212902</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12598263977358</v>
+        <v>86.15697853819346</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250037080746173</v>
+        <v>3.251206737290319</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.37368602241954</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>6.497206306705391</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="D2" t="n">
-        <v>26.36188935443535</v>
+        <v>13.59524220840983</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28505099159684</v>
+        <v>18.22614612934204</v>
       </c>
       <c r="C3" t="n">
-        <v>22.84036033930204</v>
+        <v>20.14055415262332</v>
       </c>
       <c r="D3" t="n">
-        <v>45.54327600000953</v>
+        <v>24.56823629877643</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.13354304997335</v>
+        <v>29.89029060349839</v>
       </c>
       <c r="C4" t="n">
-        <v>48.49833658979244</v>
+        <v>41.73409490753191</v>
       </c>
       <c r="D4" t="n">
-        <v>33.37451320587032</v>
+        <v>22.8835572382889</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.84831213192726</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="C5" t="n">
-        <v>34.97476196379262</v>
+        <v>26.89988709636261</v>
       </c>
       <c r="D5" t="n">
-        <v>30.80233422074368</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.45225120095506</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72644570878471</v>
+        <v>16.73916132470599</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0313188235867</v>
+        <v>102.1088840807065</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181611427196176</v>
+        <v>5.021748397411797</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.069745144730529</v>
+        <v>5.768749510154257</v>
       </c>
       <c r="C2" t="n">
-        <v>5.359360717483338</v>
+        <v>5.792311455056181</v>
       </c>
       <c r="D2" t="n">
-        <v>26.05165707989336</v>
+        <v>14.94612704945344</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.45900026169778</v>
+        <v>17.58310138306037</v>
       </c>
       <c r="C3" t="n">
-        <v>24.16081100151401</v>
+        <v>17.96107424919539</v>
       </c>
       <c r="D3" t="n">
-        <v>55.44911033585985</v>
+        <v>29.43279617331937</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>32.72361447795468</v>
       </c>
       <c r="C4" t="n">
-        <v>52.76108512163209</v>
+        <v>46.67326760759762</v>
       </c>
       <c r="D4" t="n">
-        <v>47.86020058203201</v>
+        <v>29.44359539806609</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.69724615866027</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="C5" t="n">
-        <v>64.45173678380311</v>
+        <v>54.51154127830416</v>
       </c>
       <c r="D5" t="n">
-        <v>35.31837366027901</v>
+        <v>31.34229545807943</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>34.61642405174254</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04541877556125</v>
+        <v>18.07006243901269</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7248748691377</v>
+        <v>117.8856454354637</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01513959185375</v>
+        <v>6.883833310100071</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.985134915716055</v>
+        <v>6.646431957750906</v>
       </c>
       <c r="C2" t="n">
-        <v>6.57770961845363</v>
+        <v>8.530405802200535</v>
       </c>
       <c r="D2" t="n">
-        <v>28.44908497366407</v>
+        <v>24.71746194982195</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10418842983718</v>
+        <v>16.84679060487527</v>
       </c>
       <c r="C3" t="n">
-        <v>20.88668240785089</v>
+        <v>19.39442589739574</v>
       </c>
       <c r="D3" t="n">
-        <v>59.19447782756144</v>
+        <v>32.21605091485908</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>24.50442269800039</v>
       </c>
       <c r="C4" t="n">
-        <v>47.22206457427158</v>
+        <v>38.2881604656256</v>
       </c>
       <c r="D4" t="n">
-        <v>55.81137523872692</v>
+        <v>32.13652935081509</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.13841073076558</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="C5" t="n">
-        <v>61.04016351154545</v>
+        <v>53.06346341454012</v>
       </c>
       <c r="D5" t="n">
-        <v>35.39200473809752</v>
+        <v>28.37250865273283</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.27675504160637</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="C6" t="n">
-        <v>46.73217246985243</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>22.93657161431823</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050195035644554</v>
+        <v>7.065288979719471</v>
       </c>
       <c r="C21" t="n">
-        <v>66.97685283862326</v>
+        <v>66.23708418487003</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406371897277847</v>
+        <v>5.298966734789603</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.970007789524853</v>
+        <v>5.283766144256333</v>
       </c>
       <c r="C2" t="n">
-        <v>6.450082416901544</v>
+        <v>4.147884050442774</v>
       </c>
       <c r="D2" t="n">
-        <v>24.4249011339564</v>
+        <v>20.04434287760713</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.70505908256523</v>
+        <v>20.95540474714817</v>
       </c>
       <c r="C3" t="n">
-        <v>23.99391389179205</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D3" t="n">
-        <v>68.78615289805276</v>
+        <v>45.87216148093222</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.01867856857647</v>
+        <v>30.17107044691297</v>
       </c>
       <c r="C4" t="n">
-        <v>50.51484637431538</v>
+        <v>44.58018150214342</v>
       </c>
       <c r="D4" t="n">
-        <v>73.34735273198346</v>
+        <v>42.05316291141212</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.67332436085985</v>
+        <v>32.07860623626453</v>
       </c>
       <c r="C5" t="n">
-        <v>77.18991324640548</v>
+        <v>64.37810570598461</v>
       </c>
       <c r="D5" t="n">
-        <v>48.81740459367266</v>
+        <v>34.23845118560752</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.42017232188442</v>
+        <v>25.27803988894688</v>
       </c>
       <c r="C6" t="n">
-        <v>76.35739119320418</v>
+        <v>67.09951034215676</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>32.80509953740717</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>48.92736033654828</v>
+        <v>43.05847256056086</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269696649475422</v>
+        <v>7.292193074519185</v>
       </c>
       <c r="C21" t="n">
-        <v>76.33181481949194</v>
+        <v>76.56802728245144</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452272487106567</v>
+        <v>6.380668940204287</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.434554380082843</v>
+        <v>5.067781649322035</v>
       </c>
       <c r="C2" t="n">
-        <v>3.788564390688441</v>
+        <v>5.612651625179015</v>
       </c>
       <c r="D2" t="n">
-        <v>22.68328070662255</v>
+        <v>18.58841103220911</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.69524160552276</v>
+        <v>19.49260066782042</v>
       </c>
       <c r="C3" t="n">
-        <v>24.63695863807371</v>
+        <v>20.91122610045706</v>
       </c>
       <c r="D3" t="n">
-        <v>72.36462328003239</v>
+        <v>51.2619563772472</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.66354794154638</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="C4" t="n">
-        <v>55.58164627593317</v>
+        <v>60.27832729304991</v>
       </c>
       <c r="D4" t="n">
-        <v>91.36831359113789</v>
+        <v>55.18600195112171</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.58835427894688</v>
+        <v>39.90804417763285</v>
       </c>
       <c r="C5" t="n">
-        <v>86.49197274414401</v>
+        <v>75.12824306748718</v>
       </c>
       <c r="D5" t="n">
-        <v>63.66633862040567</v>
+        <v>42.14152020479434</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>35.42145716922493</v>
       </c>
       <c r="C6" t="n">
-        <v>101.9976959850181</v>
+        <v>87.34609324683873</v>
       </c>
       <c r="D6" t="n">
-        <v>43.79380159104173</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>82.46386191361933</v>
+        <v>73.60064363967912</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>46.64774216728719</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.476700346555594</v>
+        <v>7.507851513949427</v>
       </c>
       <c r="C21" t="n">
-        <v>85.98205398538933</v>
+        <v>86.3402924104184</v>
       </c>
       <c r="D21" t="n">
-        <v>6.542112803236145</v>
+        <v>7.507851513949427</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_69_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497664364786</v>
+        <v>10.84497643560298</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907302708998</v>
+        <v>37.78907230216233</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.91895690890402</v>
+        <v>1.497165248976386</v>
       </c>
       <c r="C2" t="n">
-        <v>5.282784396552087</v>
+        <v>1.838813450054276</v>
       </c>
       <c r="D2" t="n">
-        <v>18.9133695223148</v>
+        <v>17.72938179099315</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32922963828795</v>
+        <v>13.98008730847458</v>
       </c>
       <c r="C3" t="n">
-        <v>21.40209995258047</v>
+        <v>24.12644983186537</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9863062565321</v>
+        <v>78.71653092650926</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.30543101367455</v>
+        <v>23.52169324604933</v>
       </c>
       <c r="C4" t="n">
-        <v>55.83690067903733</v>
+        <v>70.16943541333653</v>
       </c>
       <c r="D4" t="n">
-        <v>67.74451858384691</v>
+        <v>86.8758360965045</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.41841411512095</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C5" t="n">
-        <v>93.97779898902593</v>
+        <v>72.08482518432207</v>
       </c>
       <c r="D5" t="n">
-        <v>51.49266708774522</v>
+        <v>50.33911353525522</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.56487444950297</v>
+        <v>12.51826497685108</v>
       </c>
       <c r="C6" t="n">
-        <v>104.6140536168359</v>
+        <v>42.66675522656639</v>
       </c>
       <c r="D6" t="n">
-        <v>41.41895389446869</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6874637104761</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.7745421853885</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>70.93127163183205</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.710665408213788</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.41948442664562</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.674498584240512</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.542587685278997</v>
+        <v>1.151590057081509</v>
       </c>
       <c r="C2" t="n">
-        <v>15.00503191170825</v>
+        <v>5.193445355465627</v>
       </c>
       <c r="D2" t="n">
-        <v>21.03983504971339</v>
+        <v>14.29522832153781</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.08026663203676</v>
+        <v>9.125344910974103</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84741249968102</v>
+        <v>13.90645623065607</v>
       </c>
       <c r="D3" t="n">
-        <v>56.11179003622645</v>
+        <v>74.63736921536376</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.8887690764464</v>
+        <v>25.88279647476291</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57339138367169</v>
+        <v>65.16644911249479</v>
       </c>
       <c r="D4" t="n">
-        <v>78.22271183127312</v>
+        <v>106.8494931394059</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>27.4889357189107</v>
       </c>
       <c r="C5" t="n">
-        <v>97.53663441692063</v>
+        <v>104.359780961436</v>
       </c>
       <c r="D5" t="n">
-        <v>62.26734814185396</v>
+        <v>70.09678608322227</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.10451689166923</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>126.8329676593497</v>
+        <v>81.75111308033615</v>
       </c>
       <c r="D6" t="n">
-        <v>47.85921883432777</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.17824578047897</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>125.4624478642211</v>
+        <v>46.35223610830891</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>102.725171033865</v>
+        <v>34.04701038327938</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.7578114166873</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>63.5671821022767</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>35.73070769606267</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.899725393321537</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6713614615104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.874656741651922</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.887761966546375</v>
+        <v>0.5978843518863075</v>
       </c>
       <c r="C2" t="n">
-        <v>11.47859415805371</v>
+        <v>2.075414646777757</v>
       </c>
       <c r="D2" t="n">
-        <v>35.73168944376691</v>
+        <v>9.616218763097507</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.01984024272996</v>
+        <v>7.799985510240909</v>
       </c>
       <c r="C3" t="n">
-        <v>39.21591204613884</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="D3" t="n">
-        <v>58.7134214524805</v>
+        <v>72.19772617031043</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.86324363613598</v>
+        <v>28.01417074068274</v>
       </c>
       <c r="C4" t="n">
-        <v>53.25883120768522</v>
+        <v>58.08313942635404</v>
       </c>
       <c r="D4" t="n">
-        <v>85.48469959958678</v>
+        <v>118.7698737643706</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.327152636355</v>
+        <v>27.39076094848602</v>
       </c>
       <c r="C5" t="n">
-        <v>97.83115872819468</v>
+        <v>123.4302301164303</v>
       </c>
       <c r="D5" t="n">
-        <v>73.90105843717866</v>
+        <v>80.99418560036187</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.46427851978007</v>
+        <v>15.33588088803943</v>
       </c>
       <c r="C6" t="n">
-        <v>139.9147558184385</v>
+        <v>110.732305309702</v>
       </c>
       <c r="D6" t="n">
-        <v>54.54099370943156</v>
+        <v>40.05039759474864</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.17930964364123</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>150.7944838769016</v>
+        <v>48.86747372658923</v>
       </c>
       <c r="D7" t="n">
-        <v>45.39405034896402</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.88287859022092</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>132.3494080095125</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.74843590800133</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>91.52342972840887</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>55.37547925804135</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.073454135064763</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.0283578909067</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10099943571405</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.144578954431539</v>
+        <v>1.059305772882308</v>
       </c>
       <c r="C2" t="n">
-        <v>7.621307428067988</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="D2" t="n">
-        <v>28.7494997711636</v>
+        <v>9.031097131366408</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.95035713990669</v>
+        <v>4.732023934469626</v>
       </c>
       <c r="C3" t="n">
-        <v>53.51506735849363</v>
+        <v>12.23257639491526</v>
       </c>
       <c r="D3" t="n">
-        <v>65.32058350206152</v>
+        <v>63.8332357301276</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.12979598560561</v>
+        <v>21.78596330494097</v>
       </c>
       <c r="C4" t="n">
-        <v>79.00123776074084</v>
+        <v>51.4337622254904</v>
       </c>
       <c r="D4" t="n">
-        <v>82.81729108714818</v>
+        <v>127.729303313327</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.60660657470007</v>
+        <v>34.95021827118646</v>
       </c>
       <c r="C5" t="n">
-        <v>83.59581701661591</v>
+        <v>117.0243263462198</v>
       </c>
       <c r="D5" t="n">
-        <v>53.16163818496479</v>
+        <v>103.9916255723434</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00635781677777</v>
+        <v>25.23778823307276</v>
       </c>
       <c r="C6" t="n">
-        <v>99.30083504145215</v>
+        <v>155.5323982975967</v>
       </c>
       <c r="D6" t="n">
-        <v>29.86672865859647</v>
+        <v>55.02401357992099</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>93.06379187637214</v>
+        <v>104.2625879387155</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>67.42643232767094</v>
+        <v>52.1553467881118</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.861614631430205</v>
+        <v>0.5969026041820606</v>
       </c>
       <c r="C2" t="n">
-        <v>3.19166178650638</v>
+        <v>2.66544501703009</v>
       </c>
       <c r="D2" t="n">
-        <v>19.29428763156256</v>
+        <v>6.251769380643688</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.83393007372882</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="C3" t="n">
-        <v>41.84208715499906</v>
+        <v>11.56989669454866</v>
       </c>
       <c r="D3" t="n">
-        <v>73.37091467688538</v>
+        <v>57.36351835914113</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.50963453615788</v>
+        <v>16.97441780642735</v>
       </c>
       <c r="C4" t="n">
-        <v>109.2488845285851</v>
+        <v>42.53814627731005</v>
       </c>
       <c r="D4" t="n">
-        <v>95.24818051832131</v>
+        <v>132.5280860916854</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>36.52101459798135</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7172192412398</v>
+        <v>111.0847527355266</v>
       </c>
       <c r="D5" t="n">
-        <v>65.80163987714248</v>
+        <v>120.8531423927824</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>117.7763450876729</v>
+        <v>175.8192328581528</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86422538384024</v>
+        <v>69.23284810348508</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>12.15698182168825</v>
       </c>
       <c r="C7" t="n">
-        <v>116.719002810199</v>
+        <v>152.4713089557551</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>41.56130731158447</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>87.45408549430587</v>
+        <v>79.10923000820797</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
+        <v>33.45305302221006</v>
+      </c>
+      <c r="D10" t="n">
         <v>33.31069960509428</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.645630136495907</v>
+        <v>1.417643684932394</v>
       </c>
       <c r="C2" t="n">
-        <v>5.557673753741193</v>
+        <v>3.614795047036756</v>
       </c>
       <c r="D2" t="n">
-        <v>18.06415775814131</v>
+        <v>18.20258418444011</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.55565350507047</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C3" t="n">
-        <v>25.64325003492669</v>
+        <v>10.86303834749096</v>
       </c>
       <c r="D3" t="n">
-        <v>71.64794745593223</v>
+        <v>49.65679888080367</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.63497944713198</v>
+        <v>12.73719471489812</v>
       </c>
       <c r="C4" t="n">
-        <v>107.7811717107361</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="D4" t="n">
-        <v>108.8532402037736</v>
+        <v>131.3666785575614</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.60847225911733</v>
+        <v>32.32404316232624</v>
       </c>
       <c r="C5" t="n">
-        <v>158.1104677689488</v>
+        <v>94.419585455937</v>
       </c>
       <c r="D5" t="n">
-        <v>82.93313731624932</v>
+        <v>139.0400186139545</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.48437113775474</v>
+        <v>40.45291415348983</v>
       </c>
       <c r="C6" t="n">
-        <v>150.1386764104647</v>
+        <v>176.9865308785023</v>
       </c>
       <c r="D6" t="n">
-        <v>46.4504108787336</v>
+        <v>88.110874708447</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.17718191731671</v>
+        <v>23.17611805415445</v>
       </c>
       <c r="C7" t="n">
-        <v>142.4702450925929</v>
+        <v>204.15345335042</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>50.12509253572939</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>119.9155733352267</v>
+        <v>137.2728727463102</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>76.65780599070366</v>
+        <v>71.22186895228909</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>43.4874963073167</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38607319414302</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>43.39815726623026</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.75478405811655</v>
+        <v>0.9179341034707678</v>
       </c>
       <c r="C2" t="n">
-        <v>2.547635292520473</v>
+        <v>1.792671307954676</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46525060082175</v>
+        <v>12.96103319146639</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.90770002026757</v>
+        <v>4.997095814616265</v>
       </c>
       <c r="C3" t="n">
-        <v>25.314364554004</v>
+        <v>13.83282515283756</v>
       </c>
       <c r="D3" t="n">
-        <v>72.01610284502478</v>
+        <v>56.66156875060466</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.47205038595602</v>
+        <v>21.56899706230242</v>
       </c>
       <c r="C4" t="n">
-        <v>102.7016090889631</v>
+        <v>50.42550733322892</v>
       </c>
       <c r="D4" t="n">
-        <v>118.1955513573862</v>
+        <v>138.807344408048</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.96466674930968</v>
+        <v>25.77087723647878</v>
       </c>
       <c r="C5" t="n">
-        <v>190.5081420090936</v>
+        <v>144.8814174542231</v>
       </c>
       <c r="D5" t="n">
-        <v>90.41896356113125</v>
+        <v>128.8543861823939</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.48687441251096</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>187.7337229968921</v>
+        <v>184.7551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>73.45927197026759</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>153.6690411549362</v>
+        <v>96.53721525399735</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>52.48914100755572</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77302065833652</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.279037332184346</v>
+        <v>0.5163992924338223</v>
       </c>
       <c r="C2" t="n">
-        <v>3.086614782151972</v>
+        <v>1.11428364432013</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73384856115788</v>
+        <v>8.946666828801183</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.82577299245858</v>
+        <v>4.084070449666732</v>
       </c>
       <c r="C3" t="n">
-        <v>17.20512851692535</v>
+        <v>9.905834335850317</v>
       </c>
       <c r="D3" t="n">
-        <v>65.85563600087605</v>
+        <v>53.75068680751286</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.03062377194345</v>
+        <v>14.57502641724815</v>
       </c>
       <c r="C4" t="n">
-        <v>83.48095253521902</v>
+        <v>40.50887377263189</v>
       </c>
       <c r="D4" t="n">
-        <v>125.8659461706666</v>
+        <v>130.6902543893354</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.50649367106269</v>
+        <v>23.63557597974196</v>
       </c>
       <c r="C5" t="n">
-        <v>191.5880644837651</v>
+        <v>106.519625910779</v>
       </c>
       <c r="D5" t="n">
-        <v>108.6794708601219</v>
+        <v>135.2357462599982</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.71708640139023</v>
+        <v>15.05411929692059</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6709418682119</v>
+        <v>174.0884116555657</v>
       </c>
       <c r="D6" t="n">
-        <v>60.78000036992004</v>
+        <v>79.25551041614078</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.87668500435917</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>208.2856294375948</v>
+        <v>129.654510561355</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>140.5273663858884</v>
+        <v>57.24570863463151</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>65.23124446097505</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>21.85468564423824</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.478912953223196</v>
+        <v>0.5684319207589033</v>
       </c>
       <c r="C2" t="n">
-        <v>2.351285751671111</v>
+        <v>2.274709430739859</v>
       </c>
       <c r="D2" t="n">
-        <v>8.774860980557991</v>
+        <v>14.61135108230528</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.02426595516569</v>
+        <v>2.793072218582175</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92747384307275</v>
+        <v>6.46971737098648</v>
       </c>
       <c r="D3" t="n">
-        <v>61.40831890063799</v>
+        <v>48.2774433563369</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.31292514241003</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>67.77004402415733</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D4" t="n">
-        <v>129.3374060528833</v>
+        <v>128.5333546831052</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.34789251133121</v>
+        <v>23.46377013149877</v>
       </c>
       <c r="C5" t="n">
-        <v>183.3168400754857</v>
+        <v>89.09360416039806</v>
       </c>
       <c r="D5" t="n">
-        <v>122.816637801276</v>
+        <v>153.3980787885641</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.41773546705297</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="C6" t="n">
-        <v>274.798054652612</v>
+        <v>172.3575904529785</v>
       </c>
       <c r="D6" t="n">
-        <v>71.3661858648134</v>
+        <v>104.1310337463464</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>260.9858462015636</v>
+        <v>199.3026379437365</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>3.087596529856218</v>
       </c>
       <c r="C8" t="n">
-        <v>179.6647386156875</v>
+        <v>119.4148820060608</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.8874999246391163</v>
       </c>
       <c r="C9" t="n">
-        <v>77.54530591534278</v>
+        <v>52.25155806312797</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.828235209485814</v>
+        <v>1.461822331623501</v>
       </c>
       <c r="C2" t="n">
-        <v>9.513135254151592</v>
+        <v>6.674902641174064</v>
       </c>
       <c r="D2" t="n">
-        <v>11.56596970373167</v>
+        <v>20.4822023537012</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.29500733735955</v>
+        <v>2.351285751671111</v>
       </c>
       <c r="C3" t="n">
-        <v>12.20803270230909</v>
+        <v>7.853981633974484</v>
       </c>
       <c r="D3" t="n">
-        <v>55.72399969304897</v>
+        <v>48.64069000690822</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.37000537797658</v>
+        <v>7.951174656694918</v>
       </c>
       <c r="C4" t="n">
-        <v>53.19501760690918</v>
+        <v>22.60277739487432</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5205919629499</v>
+        <v>122.8411814938821</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.99798941799185</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>158.8713222397401</v>
+        <v>71.69212610262333</v>
       </c>
       <c r="D5" t="n">
-        <v>137.1992416684918</v>
+        <v>165.8171872472863</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.29197394991814</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="C6" t="n">
-        <v>282.566624236317</v>
+        <v>157.1022128766874</v>
       </c>
       <c r="D6" t="n">
-        <v>87.90961642907641</v>
+        <v>128.1612723031957</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>317.3391461730347</v>
+        <v>227.7487776742878</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>67.97130230352791</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>248.0091050468292</v>
+        <v>195.3530669295516</v>
       </c>
       <c r="D8" t="n">
         <v>38.21943812632832</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.106249736236907</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>131.2390513560093</v>
+        <v>101.1749914088593</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>54.8060655895782</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.601271563355553</v>
+        <v>4.206788912697583</v>
       </c>
       <c r="C2" t="n">
-        <v>5.862997289761952</v>
+        <v>4.068362486398782</v>
       </c>
       <c r="D2" t="n">
-        <v>7.341509332357648</v>
+        <v>10.08843940884022</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4164820107789</v>
+        <v>1.86826588118168</v>
       </c>
       <c r="C2" t="n">
-        <v>5.326963043243193</v>
+        <v>9.452266896488291</v>
       </c>
       <c r="D2" t="n">
-        <v>8.511752595819846</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>3.691371367968007</v>
       </c>
       <c r="C3" t="n">
-        <v>21.72607669498191</v>
+        <v>17.69109363052752</v>
       </c>
       <c r="D3" t="n">
-        <v>60.51492848977339</v>
+        <v>53.03401098341269</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.88121819444869</v>
+        <v>6.215444715586556</v>
       </c>
       <c r="C4" t="n">
-        <v>79.30754304446585</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D4" t="n">
-        <v>131.1752377552333</v>
+        <v>119.7270777760113</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.14781160164732</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>238.6137795171873</v>
+        <v>56.3768619163731</v>
       </c>
       <c r="D5" t="n">
-        <v>126.3509295365645</v>
+        <v>170.6522946907018</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.03023855684918</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C6" t="n">
-        <v>267.1502400365293</v>
+        <v>136.8958816278795</v>
       </c>
       <c r="D6" t="n">
-        <v>71.80895407942872</v>
+        <v>149.8569148193459</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>174.3898082007694</v>
+        <v>228.1679839440012</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>86.47626478087604</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.086213871524472</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>96.71687508387453</v>
+        <v>250.2622160280756</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>45.72980806381643</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>169.4015481154913</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>80.28732725330416</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>20.25738212942868</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.379797492823274</v>
+        <v>5.21700730036755</v>
       </c>
       <c r="C2" t="n">
-        <v>6.613052535806514</v>
+        <v>4.633849164044945</v>
       </c>
       <c r="D2" t="n">
-        <v>9.206829970426588</v>
+        <v>18.86428213710246</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.01935721664445</v>
+        <v>6.950773746067418</v>
       </c>
       <c r="C3" t="n">
-        <v>14.77039421039326</v>
+        <v>8.030696220738909</v>
       </c>
       <c r="D3" t="n">
-        <v>9.302059497738529</v>
+        <v>9.915651812892785</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39860218681659</v>
+        <v>11.67859128483829</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14562321333392</v>
+        <v>59.95010192883655</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576306139625481</v>
+        <v>0.7785727523225525</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.666246838285089</v>
+        <v>3.403719290623691</v>
       </c>
       <c r="C2" t="n">
-        <v>4.902848035008571</v>
+        <v>3.904410619789565</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52183211476957</v>
+        <v>24.39741219823749</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.90631736193583</v>
+        <v>13.98990478551705</v>
       </c>
       <c r="C3" t="n">
-        <v>21.78498155723672</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="D3" t="n">
-        <v>14.78512042595696</v>
+        <v>24.02336632291945</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.25970547773567</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C4" t="n">
-        <v>23.40682876465245</v>
+        <v>13.63058512576272</v>
       </c>
       <c r="D4" t="n">
-        <v>19.94813160259094</v>
+        <v>19.4376227963826</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44323200212902</v>
+        <v>13.6316286128312</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15697853819346</v>
+        <v>73.77116661061589</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251206737290319</v>
+        <v>1.603721013274259</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>3.364449382453819</v>
       </c>
       <c r="C2" t="n">
-        <v>4.233296100712247</v>
+        <v>4.519966430352315</v>
       </c>
       <c r="D2" t="n">
-        <v>13.59524220840983</v>
+        <v>21.55427084673872</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.22614612934204</v>
+        <v>12.79708132485717</v>
       </c>
       <c r="C3" t="n">
-        <v>20.14055415262332</v>
+        <v>15.07473599870977</v>
       </c>
       <c r="D3" t="n">
-        <v>24.56823629877643</v>
+        <v>38.71031197845173</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.89029060349839</v>
+        <v>19.73116535995239</v>
       </c>
       <c r="C4" t="n">
-        <v>41.73409490753191</v>
+        <v>28.28218786394211</v>
       </c>
       <c r="D4" t="n">
-        <v>22.8835572382889</v>
+        <v>27.32498385230147</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.30897278939726</v>
+        <v>8.369399178704059</v>
       </c>
       <c r="C5" t="n">
-        <v>26.89988709636261</v>
+        <v>17.32784697995621</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>27.09623663721197</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73916132470599</v>
+        <v>14.84630437051744</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1088840807065</v>
+        <v>87.42823684860274</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021748397411797</v>
+        <v>2.474384061752907</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.768749510154257</v>
+        <v>3.129811681138832</v>
       </c>
       <c r="C2" t="n">
-        <v>5.792311455056181</v>
+        <v>4.239186586937727</v>
       </c>
       <c r="D2" t="n">
-        <v>14.94612704945344</v>
+        <v>25.15139443509903</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.58310138306037</v>
+        <v>12.17858027118168</v>
       </c>
       <c r="C3" t="n">
-        <v>17.96107424919539</v>
+        <v>16.81733817374786</v>
       </c>
       <c r="D3" t="n">
-        <v>29.43279617331937</v>
+        <v>46.97171890968864</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.72361447795468</v>
+        <v>22.74316731658161</v>
       </c>
       <c r="C4" t="n">
-        <v>46.67326760759762</v>
+        <v>33.70634392990574</v>
       </c>
       <c r="D4" t="n">
-        <v>29.44359539806609</v>
+        <v>40.30467025014855</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.91876128692155</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="C5" t="n">
-        <v>54.51154127830416</v>
+        <v>37.94454876913922</v>
       </c>
       <c r="D5" t="n">
-        <v>31.34229545807943</v>
+        <v>31.14594591723007</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>28.29691407950582</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07006243901269</v>
+        <v>16.09749425822178</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8856454354637</v>
+        <v>101.6683847887692</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883833310100071</v>
+        <v>3.388946159625639</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.646431957750906</v>
+        <v>4.014366362665207</v>
       </c>
       <c r="C2" t="n">
-        <v>8.530405802200535</v>
+        <v>5.361324212891832</v>
       </c>
       <c r="D2" t="n">
-        <v>24.71746194982195</v>
+        <v>31.13514669248335</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84679060487527</v>
+        <v>11.4029995848267</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39442589739574</v>
+        <v>16.61117115585603</v>
       </c>
       <c r="D3" t="n">
-        <v>32.21605091485908</v>
+        <v>56.19523859108742</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.50442269800039</v>
+        <v>23.40682876465245</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2881604656256</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="D4" t="n">
-        <v>32.13652935081509</v>
+        <v>54.77759490615503</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.27371198750239</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>53.06346341454012</v>
+        <v>51.5908418581699</v>
       </c>
       <c r="D5" t="n">
-        <v>28.37250865273283</v>
+        <v>38.63177216211199</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.6516027381794</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>40.21140421824511</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>20.18178755620168</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065288979719471</v>
+        <v>17.37930538446306</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23708418487003</v>
+        <v>115.5723808066793</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298966734789603</v>
+        <v>4.344826346115765</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.283766144256333</v>
+        <v>3.351686662298611</v>
       </c>
       <c r="C2" t="n">
-        <v>4.147884050442774</v>
+        <v>7.755806863549802</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04434287760713</v>
+        <v>32.95923392697392</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.95540474714817</v>
+        <v>12.7283589855599</v>
       </c>
       <c r="C3" t="n">
-        <v>28.53940576245478</v>
+        <v>18.96736564604837</v>
       </c>
       <c r="D3" t="n">
-        <v>45.87216148093222</v>
+        <v>67.35770998837366</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.17107044691297</v>
+        <v>22.52620107394306</v>
       </c>
       <c r="C4" t="n">
-        <v>44.58018150214342</v>
+        <v>40.20256848890688</v>
       </c>
       <c r="D4" t="n">
-        <v>42.05316291141212</v>
+        <v>69.76102836836986</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.07860623626453</v>
+        <v>31.46501392111028</v>
       </c>
       <c r="C5" t="n">
-        <v>64.37810570598461</v>
+        <v>61.99736752318609</v>
       </c>
       <c r="D5" t="n">
-        <v>34.23845118560752</v>
+        <v>48.96466674930968</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.27803988894688</v>
+        <v>27.08936440328224</v>
       </c>
       <c r="C6" t="n">
-        <v>67.09951034215676</v>
+        <v>62.22905998138833</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80509953740717</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>43.05847256056086</v>
+        <v>41.86074036137975</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>23.86628669023996</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.292193074519185</v>
+        <v>18.68527227124289</v>
       </c>
       <c r="C21" t="n">
-        <v>76.56802728245144</v>
+        <v>129.0173561585819</v>
       </c>
       <c r="D21" t="n">
-        <v>6.380668940204287</v>
+        <v>5.338649220355111</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.067781649322035</v>
+        <v>3.049308369390593</v>
       </c>
       <c r="C2" t="n">
-        <v>5.612651625179015</v>
+        <v>4.653484118129881</v>
       </c>
       <c r="D2" t="n">
-        <v>18.58841103220911</v>
+        <v>25.70510014029423</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49260066782042</v>
+        <v>16.38046044535803</v>
       </c>
       <c r="C3" t="n">
-        <v>20.91122610045706</v>
+        <v>30.86123908299849</v>
       </c>
       <c r="D3" t="n">
-        <v>51.2619563772472</v>
+        <v>75.18223919122073</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.30993884156828</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="C4" t="n">
-        <v>60.27832729304991</v>
+        <v>56.80686741083319</v>
       </c>
       <c r="D4" t="n">
-        <v>55.18600195112171</v>
+        <v>65.07711007140833</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.90804417763285</v>
+        <v>15.24163310843173</v>
       </c>
       <c r="C5" t="n">
-        <v>75.12824306748718</v>
+        <v>37.18369429834795</v>
       </c>
       <c r="D5" t="n">
-        <v>42.14152020479434</v>
+        <v>38.26361677301944</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.42145716922493</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>87.34609324683873</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>26.04282135055514</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>73.60064363967912</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55876297909923</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.507851513949427</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.3402924104184</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.507851513949427</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
